--- a/utenti.xlsx
+++ b/utenti.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B60AE32-86CF-41C7-9429-A2895F0C3E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5101E39-FEEC-46A7-A4A6-E9F39AE906A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{38FE3314-E022-4CA1-9956-19B554EBCB7E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>username</t>
   </si>
@@ -81,6 +81,18 @@
   </si>
   <si>
     <t>C000177 - GRISPORT SPA</t>
+  </si>
+  <si>
+    <t>data</t>
+  </si>
+  <si>
+    <t>spirale</t>
+  </si>
+  <si>
+    <t>SPI987</t>
+  </si>
+  <si>
+    <t>C000744 - SPIRALE SRL</t>
   </si>
 </sst>
 </file>
@@ -102,12 +114,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -148,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -156,6 +174,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -493,14 +519,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E837CC2E-FFAA-493E-9E03-C350178C8C16}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="19.28515625" customWidth="1"/>
     <col min="3" max="3" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -510,9 +537,11 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1"/>
+      <c r="D1" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -522,7 +551,9 @@
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="1"/>
+      <c r="D2" s="5">
+        <v>46077</v>
+      </c>
     </row>
     <row r="3" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -534,9 +565,11 @@
       <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="1"/>
+      <c r="D3" s="5">
+        <v>46077</v>
+      </c>
     </row>
-    <row r="4" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -546,7 +579,9 @@
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="1"/>
+      <c r="D4" s="5">
+        <v>46077</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -555,8 +590,25 @@
       <c r="B5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="4" t="s">
         <v>14</v>
+      </c>
+      <c r="D5" s="6">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="6">
+        <v>46078</v>
       </c>
     </row>
   </sheetData>

--- a/utenti.xlsx
+++ b/utenti.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5101E39-FEEC-46A7-A4A6-E9F39AE906A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1740674D-CF5A-4227-8B0A-78DB43E1AB96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{38FE3314-E022-4CA1-9956-19B554EBCB7E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
   <si>
     <t>username</t>
   </si>
@@ -93,6 +93,9 @@
   </si>
   <si>
     <t>C000744 - SPIRALE SRL</t>
+  </si>
+  <si>
+    <t>test</t>
   </si>
 </sst>
 </file>
@@ -519,7 +522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E837CC2E-FFAA-493E-9E03-C350178C8C16}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="19.28515625" customWidth="1"/>
@@ -611,6 +614,17 @@
         <v>46078</v>
       </c>
     </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/utenti.xlsx
+++ b/utenti.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1740674D-CF5A-4227-8B0A-78DB43E1AB96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC719A6-80ED-41EB-93C8-CCD42494C9F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{38FE3314-E022-4CA1-9956-19B554EBCB7E}"/>
+    <workbookView xWindow="1380" yWindow="3600" windowWidth="15030" windowHeight="12000" xr2:uid="{38FE3314-E022-4CA1-9956-19B554EBCB7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>username</t>
   </si>
@@ -95,7 +95,10 @@
     <t>C000744 - SPIRALE SRL</t>
   </si>
   <si>
-    <t>test</t>
+    <t>nikola</t>
+  </si>
+  <si>
+    <t>nik001</t>
   </si>
 </sst>
 </file>
@@ -169,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -186,6 +189,9 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -619,10 +625,13 @@
         <v>19</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
+      </c>
+      <c r="D7" s="8">
+        <v>46078</v>
       </c>
     </row>
   </sheetData>

--- a/utenti.xlsx
+++ b/utenti.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC719A6-80ED-41EB-93C8-CCD42494C9F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB4EEC14-7352-4D24-B35D-5F6ECFFE5275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1380" yWindow="3600" windowWidth="15030" windowHeight="12000" xr2:uid="{38FE3314-E022-4CA1-9956-19B554EBCB7E}"/>
   </bookViews>

--- a/utenti.xlsx
+++ b/utenti.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB4EEC14-7352-4D24-B35D-5F6ECFFE5275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F310C3F-8A87-4DB6-9159-30F45335E322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="3600" windowWidth="15030" windowHeight="12000" xr2:uid="{38FE3314-E022-4CA1-9956-19B554EBCB7E}"/>
+    <workbookView xWindow="5880" yWindow="1995" windowWidth="15030" windowHeight="12000" xr2:uid="{38FE3314-E022-4CA1-9956-19B554EBCB7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
   <si>
     <t>username</t>
   </si>
@@ -95,17 +95,23 @@
     <t>C000744 - SPIRALE SRL</t>
   </si>
   <si>
-    <t>nikola</t>
-  </si>
-  <si>
-    <t>nik001</t>
+    <t>Nikola</t>
+  </si>
+  <si>
+    <t>Nik001</t>
+  </si>
+  <si>
+    <t>valentina</t>
+  </si>
+  <si>
+    <t>val222</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -114,6 +120,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -172,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -187,11 +200,10 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -528,7 +540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E837CC2E-FFAA-493E-9E03-C350178C8C16}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="19.28515625" customWidth="1"/>
@@ -537,16 +549,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="7" t="s">
         <v>15</v>
       </c>
     </row>
@@ -575,7 +587,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="5">
-        <v>46077</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -589,10 +601,10 @@
         <v>11</v>
       </c>
       <c r="D4" s="5">
-        <v>46077</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46079</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>12</v>
       </c>
@@ -602,39 +614,54 @@
       <c r="C5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="6">
-        <v>46078</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="D5" s="5">
+        <v>46080</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="6">
-        <v>46078</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+      <c r="D6" s="5">
+        <v>46081</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="8">
-        <v>46078</v>
+      <c r="D7" s="5">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="5">
+        <v>46083</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/utenti.xlsx
+++ b/utenti.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F310C3F-8A87-4DB6-9159-30F45335E322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96E9F9D7-4FC6-4B2C-83BA-8B22153BDA68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5880" yWindow="1995" windowWidth="15030" windowHeight="12000" xr2:uid="{38FE3314-E022-4CA1-9956-19B554EBCB7E}"/>
+    <workbookView xWindow="14775" yWindow="3405" windowWidth="9240" windowHeight="8730" xr2:uid="{38FE3314-E022-4CA1-9956-19B554EBCB7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -98,13 +98,13 @@
     <t>Nikola</t>
   </si>
   <si>
-    <t>Nik001</t>
-  </si>
-  <si>
     <t>valentina</t>
   </si>
   <si>
     <t>val222</t>
+  </si>
+  <si>
+    <t>Nik789</t>
   </si>
 </sst>
 </file>
@@ -633,11 +633,11 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>20</v>
+      <c r="B7" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
@@ -648,10 +648,10 @@
     </row>
     <row r="8" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>22</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>

--- a/utenti.xlsx
+++ b/utenti.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96E9F9D7-4FC6-4B2C-83BA-8B22153BDA68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3FE09FA-B128-4569-B10E-69F032DC636D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14775" yWindow="3405" windowWidth="9240" windowHeight="8730" xr2:uid="{38FE3314-E022-4CA1-9956-19B554EBCB7E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{38FE3314-E022-4CA1-9956-19B554EBCB7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
   <si>
     <t>username</t>
   </si>
@@ -105,6 +105,12 @@
   </si>
   <si>
     <t>Nik789</t>
+  </si>
+  <si>
+    <t>pippo</t>
+  </si>
+  <si>
+    <t>pip963</t>
   </si>
 </sst>
 </file>
@@ -540,7 +546,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E837CC2E-FFAA-493E-9E03-C350178C8C16}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="19.28515625" customWidth="1"/>
@@ -660,6 +666,20 @@
         <v>46083</v>
       </c>
     </row>
+    <row r="9" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="5">
+        <v>46084</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/utenti.xlsx
+++ b/utenti.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3FE09FA-B128-4569-B10E-69F032DC636D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B7DA4F-DCBE-4E9A-B31F-AF81692D102D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{38FE3314-E022-4CA1-9956-19B554EBCB7E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
   <si>
     <t>username</t>
   </si>
@@ -56,15 +56,6 @@
     <t>TUTTI</t>
   </si>
   <si>
-    <t>gar_demo</t>
-  </si>
-  <si>
-    <t>gar789</t>
-  </si>
-  <si>
-    <t>C000161 - GARSPORT SRL</t>
-  </si>
-  <si>
     <t>annic_demo</t>
   </si>
   <si>
@@ -95,29 +86,23 @@
     <t>C000744 - SPIRALE SRL</t>
   </si>
   <si>
-    <t>Nikola</t>
+    <t>nikola</t>
+  </si>
+  <si>
+    <t>nikola2026</t>
   </si>
   <si>
     <t>valentina</t>
   </si>
   <si>
-    <t>val222</t>
-  </si>
-  <si>
-    <t>Nik789</t>
-  </si>
-  <si>
-    <t>pippo</t>
-  </si>
-  <si>
-    <t>pip963</t>
+    <t>vale2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -126,13 +111,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -191,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -206,10 +184,11 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -546,7 +525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E837CC2E-FFAA-493E-9E03-C350178C8C16}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="19.28515625" customWidth="1"/>
@@ -555,17 +534,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>15</v>
+      <c r="D1" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -584,104 +563,75 @@
     </row>
     <row r="3" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D3" s="5">
-        <v>46078</v>
+        <v>46077</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="5">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="5">
-        <v>46079</v>
+      <c r="D5" s="6">
+        <v>46078</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="3" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="B6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="5">
-        <v>46080</v>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="6">
+        <v>46078</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="5">
-        <v>46081</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="B7" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="5">
-        <v>46082</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="5">
-        <v>46083</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="5">
-        <v>46084</v>
+      <c r="D7" s="8">
+        <v>46078</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/utenti.xlsx
+++ b/utenti.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B7DA4F-DCBE-4E9A-B31F-AF81692D102D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD557C16-4412-4B4B-AD8F-BB21ED44F476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{38FE3314-E022-4CA1-9956-19B554EBCB7E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
   <si>
     <t>username</t>
   </si>
@@ -96,6 +96,12 @@
   </si>
   <si>
     <t>vale2026</t>
+  </si>
+  <si>
+    <t>stefano</t>
+  </si>
+  <si>
+    <t>ste123</t>
   </si>
 </sst>
 </file>
@@ -525,7 +531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E837CC2E-FFAA-493E-9E03-C350178C8C16}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="19.28515625" customWidth="1"/>
@@ -631,6 +637,20 @@
         <v>46078</v>
       </c>
     </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="6">
+        <v>46078</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/utenti.xlsx
+++ b/utenti.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD557C16-4412-4B4B-AD8F-BB21ED44F476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC0A0A8-A6E6-4196-A031-170938C037D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{38FE3314-E022-4CA1-9956-19B554EBCB7E}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11385" xr2:uid="{38FE3314-E022-4CA1-9956-19B554EBCB7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
+    <sheet name="Foglio2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,16 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
-  <si>
-    <t>username</t>
-  </si>
-  <si>
-    <t>password</t>
-  </si>
-  <si>
-    <t>cliente_arca</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="89">
   <si>
     <t>safit_admin</t>
   </si>
@@ -56,52 +48,262 @@
     <t>TUTTI</t>
   </si>
   <si>
-    <t>annic_demo</t>
-  </si>
-  <si>
-    <t>annic456</t>
-  </si>
-  <si>
     <t>C000004 - ANNIC S.A.S.</t>
   </si>
   <si>
     <t>grisport</t>
   </si>
   <si>
-    <t>gri2026</t>
-  </si>
-  <si>
     <t>C000177 - GRISPORT SPA</t>
   </si>
   <si>
-    <t>data</t>
-  </si>
-  <si>
     <t>spirale</t>
   </si>
   <si>
-    <t>SPI987</t>
-  </si>
-  <si>
     <t>C000744 - SPIRALE SRL</t>
   </si>
   <si>
     <t>nikola</t>
   </si>
   <si>
-    <t>nikola2026</t>
-  </si>
-  <si>
-    <t>valentina</t>
-  </si>
-  <si>
-    <t>vale2026</t>
-  </si>
-  <si>
-    <t>stefano</t>
-  </si>
-  <si>
-    <t>ste123</t>
+    <t>Username</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>Data Agg.</t>
+  </si>
+  <si>
+    <t>annic</t>
+  </si>
+  <si>
+    <t>lasportiva</t>
+  </si>
+  <si>
+    <t>C000115 - LA SPORTIVA SPA</t>
+  </si>
+  <si>
+    <t>scarpa</t>
+  </si>
+  <si>
+    <t>C000185 - S.C.A.R.P.A. SPA</t>
+  </si>
+  <si>
+    <t>aku</t>
+  </si>
+  <si>
+    <t>C000454 - AKU ITALIA SRL</t>
+  </si>
+  <si>
+    <t>meindl</t>
+  </si>
+  <si>
+    <t>C000851 - MEINDL GMBH &amp; CO. KG</t>
+  </si>
+  <si>
+    <t>lowa</t>
+  </si>
+  <si>
+    <t>C001022 - LOWA SPORTSCHUHE GMBH</t>
+  </si>
+  <si>
+    <t>asolo</t>
+  </si>
+  <si>
+    <t>C001255 - ASOLO SRL</t>
+  </si>
+  <si>
+    <t>crispi</t>
+  </si>
+  <si>
+    <t>C001488 - CRISPI SPORT SRL</t>
+  </si>
+  <si>
+    <t>cliente_arca (Ragione Sociale per Filtro)</t>
+  </si>
+  <si>
+    <t>ann482</t>
+  </si>
+  <si>
+    <t>diadora</t>
+  </si>
+  <si>
+    <t>dia915</t>
+  </si>
+  <si>
+    <t>C000050 - DIADORA SPA</t>
+  </si>
+  <si>
+    <t>las273</t>
+  </si>
+  <si>
+    <t>dolomite</t>
+  </si>
+  <si>
+    <t>dol559</t>
+  </si>
+  <si>
+    <t>C000120 - DOLOMITE SRL</t>
+  </si>
+  <si>
+    <t>gri631</t>
+  </si>
+  <si>
+    <t>sca148</t>
+  </si>
+  <si>
+    <t>salewa</t>
+  </si>
+  <si>
+    <t>sal390</t>
+  </si>
+  <si>
+    <t>C000190 - SALEWA - OBER ALP SPA</t>
+  </si>
+  <si>
+    <t>garmont</t>
+  </si>
+  <si>
+    <t>gar722</t>
+  </si>
+  <si>
+    <t>C000210 - GARMONT INTERNATIONAL</t>
+  </si>
+  <si>
+    <t>salomon</t>
+  </si>
+  <si>
+    <t>sal814</t>
+  </si>
+  <si>
+    <t>C000330 - SALOMON SAS</t>
+  </si>
+  <si>
+    <t>tecnica</t>
+  </si>
+  <si>
+    <t>tec506</t>
+  </si>
+  <si>
+    <t>C000440 - TECNICA GROUP SPA</t>
+  </si>
+  <si>
+    <t>aku925</t>
+  </si>
+  <si>
+    <t>fitwell</t>
+  </si>
+  <si>
+    <t>fit117</t>
+  </si>
+  <si>
+    <t>C000550 - FITWELL SRL</t>
+  </si>
+  <si>
+    <t>zamberlan</t>
+  </si>
+  <si>
+    <t>zam684</t>
+  </si>
+  <si>
+    <t>C000620 - ZAMBERLAN CALZATURIFICIO</t>
+  </si>
+  <si>
+    <t>spi331</t>
+  </si>
+  <si>
+    <t>mei497</t>
+  </si>
+  <si>
+    <t>kayland</t>
+  </si>
+  <si>
+    <t>kay208</t>
+  </si>
+  <si>
+    <t>C000990 - KAYLAND S.R.L.</t>
+  </si>
+  <si>
+    <t>low714</t>
+  </si>
+  <si>
+    <t>mammut</t>
+  </si>
+  <si>
+    <t>mam552</t>
+  </si>
+  <si>
+    <t>C001100 - MAMMUT SPORTS GROUP</t>
+  </si>
+  <si>
+    <t>aso836</t>
+  </si>
+  <si>
+    <t>cri194</t>
+  </si>
+  <si>
+    <t>nik2026</t>
+  </si>
+  <si>
+    <t>ann742</t>
+  </si>
+  <si>
+    <t>dia518</t>
+  </si>
+  <si>
+    <t>las903</t>
+  </si>
+  <si>
+    <t>dol336</t>
+  </si>
+  <si>
+    <t>gri612</t>
+  </si>
+  <si>
+    <t>sca229</t>
+  </si>
+  <si>
+    <t>sal841</t>
+  </si>
+  <si>
+    <t>gar115</t>
+  </si>
+  <si>
+    <t>sal907</t>
+  </si>
+  <si>
+    <t>tec442</t>
+  </si>
+  <si>
+    <t>aku681</t>
+  </si>
+  <si>
+    <t>fit550</t>
+  </si>
+  <si>
+    <t>zam319</t>
+  </si>
+  <si>
+    <t>spi208</t>
+  </si>
+  <si>
+    <t>mei914</t>
+  </si>
+  <si>
+    <t>kay732</t>
+  </si>
+  <si>
+    <t>low118</t>
+  </si>
+  <si>
+    <t>mam604</t>
+  </si>
+  <si>
+    <t>aso427</t>
+  </si>
+  <si>
+    <t>cri883</t>
   </si>
 </sst>
 </file>
@@ -531,7 +733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E837CC2E-FFAA-493E-9E03-C350178C8C16}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="19.28515625" customWidth="1"/>
@@ -539,119 +741,668 @@
     <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="D2" s="5">
-        <v>46077</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="D3" s="5">
-        <v>46077</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>71</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D4" s="5">
-        <v>46077</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="D5" s="6">
-        <v>46078</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D6" s="6">
-        <v>46078</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D7" s="8">
-        <v>46078</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="6">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="6">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="6">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="6">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="6">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="6">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="6">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="6">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" t="s">
         <v>20</v>
       </c>
-      <c r="B8" t="s">
+      <c r="D16" s="6">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" s="6">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>21</v>
       </c>
-      <c r="C8" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="6">
-        <v>46078</v>
+      <c r="B18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="6">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" s="6">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="6">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="6">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" s="6">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" s="6">
+        <v>46084</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5537FED3-508B-40DC-8B02-704FC4157F2A}">
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="6">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="6">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="6">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="6">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="6">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="6">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="6">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="6">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="6">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="6">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="6">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="6">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="6">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="6">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="6">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" s="6">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="6">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" s="6">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="6">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="6">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" s="6">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" s="6">
+        <v>46084</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>
--- a/utenti.xlsx
+++ b/utenti.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC0A0A8-A6E6-4196-A031-170938C037D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{064DFC9D-2108-4FB2-9799-57ECD25AAEFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11385" xr2:uid="{38FE3314-E022-4CA1-9956-19B554EBCB7E}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
   <si>
     <t>safit_admin</t>
   </si>
@@ -304,6 +304,15 @@
   </si>
   <si>
     <t>cri883</t>
+  </si>
+  <si>
+    <t>username</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>cliente_arca</t>
   </si>
 </sst>
 </file>
@@ -741,15 +750,15 @@
     <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>89</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>91</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>11</v>

--- a/utenti.xlsx
+++ b/utenti.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{064DFC9D-2108-4FB2-9799-57ECD25AAEFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17565760-DE4C-4FAA-95C5-783EC43F4A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11385" xr2:uid="{38FE3314-E022-4CA1-9956-19B554EBCB7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
-    <sheet name="Foglio2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="69">
   <si>
     <t>safit_admin</t>
   </si>
@@ -66,15 +65,6 @@
     <t>nikola</t>
   </si>
   <si>
-    <t>Username</t>
-  </si>
-  <si>
-    <t>Password</t>
-  </si>
-  <si>
-    <t>Data Agg.</t>
-  </si>
-  <si>
     <t>annic</t>
   </si>
   <si>
@@ -120,129 +110,66 @@
     <t>C001488 - CRISPI SPORT SRL</t>
   </si>
   <si>
-    <t>cliente_arca (Ragione Sociale per Filtro)</t>
-  </si>
-  <si>
-    <t>ann482</t>
-  </si>
-  <si>
     <t>diadora</t>
   </si>
   <si>
-    <t>dia915</t>
-  </si>
-  <si>
     <t>C000050 - DIADORA SPA</t>
   </si>
   <si>
-    <t>las273</t>
-  </si>
-  <si>
     <t>dolomite</t>
   </si>
   <si>
-    <t>dol559</t>
-  </si>
-  <si>
     <t>C000120 - DOLOMITE SRL</t>
   </si>
   <si>
-    <t>gri631</t>
-  </si>
-  <si>
-    <t>sca148</t>
-  </si>
-  <si>
     <t>salewa</t>
   </si>
   <si>
-    <t>sal390</t>
-  </si>
-  <si>
     <t>C000190 - SALEWA - OBER ALP SPA</t>
   </si>
   <si>
     <t>garmont</t>
   </si>
   <si>
-    <t>gar722</t>
-  </si>
-  <si>
     <t>C000210 - GARMONT INTERNATIONAL</t>
   </si>
   <si>
     <t>salomon</t>
   </si>
   <si>
-    <t>sal814</t>
-  </si>
-  <si>
     <t>C000330 - SALOMON SAS</t>
   </si>
   <si>
     <t>tecnica</t>
   </si>
   <si>
-    <t>tec506</t>
-  </si>
-  <si>
     <t>C000440 - TECNICA GROUP SPA</t>
   </si>
   <si>
-    <t>aku925</t>
-  </si>
-  <si>
     <t>fitwell</t>
   </si>
   <si>
-    <t>fit117</t>
-  </si>
-  <si>
     <t>C000550 - FITWELL SRL</t>
   </si>
   <si>
     <t>zamberlan</t>
   </si>
   <si>
-    <t>zam684</t>
-  </si>
-  <si>
     <t>C000620 - ZAMBERLAN CALZATURIFICIO</t>
   </si>
   <si>
-    <t>spi331</t>
-  </si>
-  <si>
-    <t>mei497</t>
-  </si>
-  <si>
     <t>kayland</t>
   </si>
   <si>
-    <t>kay208</t>
-  </si>
-  <si>
     <t>C000990 - KAYLAND S.R.L.</t>
   </si>
   <si>
-    <t>low714</t>
-  </si>
-  <si>
     <t>mammut</t>
   </si>
   <si>
-    <t>mam552</t>
-  </si>
-  <si>
     <t>C001100 - MAMMUT SPORTS GROUP</t>
   </si>
   <si>
-    <t>aso836</t>
-  </si>
-  <si>
-    <t>cri194</t>
-  </si>
-  <si>
     <t>nik2026</t>
   </si>
   <si>
@@ -313,6 +240,9 @@
   </si>
   <si>
     <t>cliente_arca</t>
+  </si>
+  <si>
+    <t>data</t>
   </si>
 </sst>
 </file>
@@ -752,24 +682,24 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>3</v>
@@ -780,13 +710,13 @@
     </row>
     <row r="3" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D3" s="5">
         <v>46084</v>
@@ -794,13 +724,13 @@
     </row>
     <row r="4" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D4" s="5">
         <v>46084</v>
@@ -808,13 +738,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D5" s="6">
         <v>46084</v>
@@ -825,7 +755,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -836,13 +766,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D7" s="8">
         <v>46084</v>
@@ -850,13 +780,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="D8" s="6">
         <v>46084</v>
@@ -864,13 +794,13 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D9" s="6">
         <v>46084</v>
@@ -878,13 +808,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="D10" s="6">
         <v>46084</v>
@@ -892,13 +822,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="D11" s="6">
         <v>46084</v>
@@ -906,13 +836,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D12" s="6">
         <v>46084</v>
@@ -920,13 +850,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="D13" s="6">
         <v>46084</v>
@@ -934,13 +864,13 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="D14" s="6">
         <v>46084</v>
@@ -951,7 +881,7 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="C15" t="s">
         <v>7</v>
@@ -962,13 +892,13 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D16" s="6">
         <v>46084</v>
@@ -976,13 +906,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="D17" s="6">
         <v>46084</v>
@@ -990,13 +920,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="C18" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D18" s="6">
         <v>46084</v>
@@ -1004,13 +934,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="C19" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="D19" s="6">
         <v>46084</v>
@@ -1018,13 +948,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D20" s="6">
         <v>46084</v>
@@ -1032,13 +962,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="C21" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D21" s="6">
         <v>46084</v>
@@ -1063,7 +993,7 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
         <v>2</v>
@@ -1075,343 +1005,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5537FED3-508B-40DC-8B02-704FC4157F2A}">
-  <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="6">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" s="6">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="6">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="6">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="6">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="6">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" s="6">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="6">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" s="6">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" t="s">
-        <v>49</v>
-      </c>
-      <c r="D11" s="6">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="6">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>51</v>
-      </c>
-      <c r="B13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" s="6">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>54</v>
-      </c>
-      <c r="B14" t="s">
-        <v>55</v>
-      </c>
-      <c r="C14" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" s="6">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="6">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C16" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="6">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>59</v>
-      </c>
-      <c r="B17" t="s">
-        <v>60</v>
-      </c>
-      <c r="C17" t="s">
-        <v>61</v>
-      </c>
-      <c r="D17" s="6">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="6">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>63</v>
-      </c>
-      <c r="B19" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" t="s">
-        <v>65</v>
-      </c>
-      <c r="D19" s="6">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" t="s">
-        <v>66</v>
-      </c>
-      <c r="C20" t="s">
-        <v>24</v>
-      </c>
-      <c r="D20" s="6">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" t="s">
-        <v>67</v>
-      </c>
-      <c r="C21" t="s">
-        <v>26</v>
-      </c>
-      <c r="D21" s="6">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>0</v>
-      </c>
-      <c r="B22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D22" s="6">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" t="s">
-        <v>68</v>
-      </c>
-      <c r="C23" t="s">
-        <v>2</v>
-      </c>
-      <c r="D23" s="6">
-        <v>46084</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
-</worksheet>
 </file>
--- a/utenti.xlsx
+++ b/utenti.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17565760-DE4C-4FAA-95C5-783EC43F4A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A078E16-E418-4B79-A1FA-B7B99FAD200F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11385" xr2:uid="{38FE3314-E022-4CA1-9956-19B554EBCB7E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{38FE3314-E022-4CA1-9956-19B554EBCB7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="71">
   <si>
     <t>safit_admin</t>
   </si>
@@ -243,6 +243,12 @@
   </si>
   <si>
     <t>data</t>
+  </si>
+  <si>
+    <t>stefano</t>
+  </si>
+  <si>
+    <t>ste123</t>
   </si>
 </sst>
 </file>
@@ -672,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E837CC2E-FFAA-493E-9E03-C350178C8C16}">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="19.28515625" customWidth="1"/>
@@ -1002,6 +1008,17 @@
         <v>46084</v>
       </c>
     </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" t="s">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/utenti.xlsx
+++ b/utenti.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A078E16-E418-4B79-A1FA-B7B99FAD200F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF75F99-9BF2-45A1-BDE8-2FDB021E63F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{38FE3314-E022-4CA1-9956-19B554EBCB7E}"/>
+    <workbookView xWindow="1140" yWindow="1140" windowWidth="26100" windowHeight="13320" xr2:uid="{38FE3314-E022-4CA1-9956-19B554EBCB7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="377">
   <si>
     <t>safit_admin</t>
   </si>
@@ -245,17 +245,935 @@
     <t>data</t>
   </si>
   <si>
+    <t>03/03/2026</t>
+  </si>
+  <si>
+    <t>gra</t>
+  </si>
+  <si>
+    <t>gra754</t>
+  </si>
+  <si>
+    <t>C000002 - GRAND INTERNATIONAL</t>
+  </si>
+  <si>
+    <t>pan</t>
+  </si>
+  <si>
+    <t>pan214</t>
+  </si>
+  <si>
+    <t>C000018 - PANTHER SRL</t>
+  </si>
+  <si>
+    <t>bas</t>
+  </si>
+  <si>
+    <t>bas125</t>
+  </si>
+  <si>
+    <t>C000038 - BASE PROTECTION SRL</t>
+  </si>
+  <si>
+    <t>boo</t>
+  </si>
+  <si>
+    <t>boo859</t>
+  </si>
+  <si>
+    <t>C000062 - BOOTS COMPANY SRL</t>
+  </si>
+  <si>
+    <t>cal</t>
+  </si>
+  <si>
+    <t>cal381</t>
+  </si>
+  <si>
+    <t>C000071 - CALZATURIFICIO 5BI SRL</t>
+  </si>
+  <si>
+    <t>sch</t>
+  </si>
+  <si>
+    <t>sch350</t>
+  </si>
+  <si>
+    <t>C000086 - Schomburg &amp; Graf GmbH &amp; Co. KG</t>
+  </si>
+  <si>
+    <t>coo</t>
+  </si>
+  <si>
+    <t>coo328</t>
+  </si>
+  <si>
+    <t>C000088 - COOPERATIVA CALZ.CALTAVUTURESE ARL</t>
+  </si>
+  <si>
+    <t>duc</t>
+  </si>
+  <si>
+    <t>duc242</t>
+  </si>
+  <si>
+    <t>C000106 - DUCATEX S.C. SA</t>
+  </si>
+  <si>
+    <t>ftg</t>
+  </si>
+  <si>
+    <t>ftg854</t>
+  </si>
+  <si>
+    <t>C000139 - F.T.G. Safety Shoes SRL</t>
+  </si>
+  <si>
+    <t>gai</t>
+  </si>
+  <si>
+    <t>gai204</t>
+  </si>
+  <si>
+    <t>C000157 - GAIBANA CALZATURE SNC di Vinco P., A., e F.lli</t>
+  </si>
+  <si>
+    <t>gar</t>
+  </si>
+  <si>
+    <t>gar792</t>
+  </si>
+  <si>
+    <t>C000161 - GARSPORT SRL</t>
+  </si>
+  <si>
+    <t>gro</t>
+  </si>
+  <si>
+    <t>gro858</t>
+  </si>
+  <si>
+    <t>C000178 - GRO.NELL S.R.L. CALZATUR.ARTIGIANO</t>
+  </si>
+  <si>
+    <t>gua</t>
+  </si>
+  <si>
+    <t>gua658</t>
+  </si>
+  <si>
+    <t>C000180 - GUADAGNIN A. &amp; FIGLIO SRL</t>
+  </si>
+  <si>
+    <t>icc</t>
+  </si>
+  <si>
+    <t>icc189</t>
+  </si>
+  <si>
+    <t>C000188 - ICC-INDUSTRIAS COMERCIO DE CALCADO</t>
+  </si>
+  <si>
+    <t>jun</t>
+  </si>
+  <si>
+    <t>jun704</t>
+  </si>
+  <si>
+    <t>C000207 - JUNIORTECH SRL</t>
+  </si>
+  <si>
+    <t>dun</t>
+  </si>
+  <si>
+    <t>dun532</t>
+  </si>
+  <si>
+    <t>C000216 - DUNLOP PROTECTIVE FOOTWEAR B.V.</t>
+  </si>
+  <si>
+    <t>lew</t>
+  </si>
+  <si>
+    <t>lew132</t>
+  </si>
+  <si>
+    <t>C000227 - LEWER Calzature Tecniche SRL</t>
+  </si>
+  <si>
+    <t>mgs</t>
+  </si>
+  <si>
+    <t>mgs130</t>
+  </si>
+  <si>
+    <t>C000235 - M &amp; G  SRL</t>
+  </si>
+  <si>
+    <t>mee</t>
+  </si>
+  <si>
+    <t>mee195</t>
+  </si>
+  <si>
+    <t>C000255 - MEET ITALIA S.r.l.</t>
+  </si>
+  <si>
+    <t>cal2</t>
+  </si>
+  <si>
+    <t>cal323</t>
+  </si>
+  <si>
+    <t>C000271 - CALZATURIFICIO MONTEBOVE S.r.l.</t>
+  </si>
+  <si>
+    <t>ori</t>
+  </si>
+  <si>
+    <t>ori338</t>
+  </si>
+  <si>
+    <t>C000289 - ORION CALZATURIFICIO SPA</t>
+  </si>
+  <si>
+    <t>ova</t>
+  </si>
+  <si>
+    <t>ova617</t>
+  </si>
+  <si>
+    <t>C000295 - OVAC S.P.A.</t>
+  </si>
+  <si>
+    <t>ove</t>
+  </si>
+  <si>
+    <t>ove716</t>
+  </si>
+  <si>
+    <t>C000296 - OVER TEAK SRL</t>
+  </si>
+  <si>
+    <t>pam</t>
+  </si>
+  <si>
+    <t>pam127</t>
+  </si>
+  <si>
+    <t>C000302 - PAMACOM SRL</t>
+  </si>
+  <si>
+    <t>cal3</t>
+  </si>
+  <si>
+    <t>cal674</t>
+  </si>
+  <si>
+    <t>C000304 - CALZATURIFICIO PANDA SPORT SRL</t>
+  </si>
+  <si>
+    <t>pez</t>
+  </si>
+  <si>
+    <t>pez303</t>
+  </si>
+  <si>
+    <t>C000308 - PEZZOL INDUSTRIES S.R.L.</t>
+  </si>
+  <si>
+    <t>yon</t>
+  </si>
+  <si>
+    <t>yon833</t>
+  </si>
+  <si>
+    <t>C000316 - YONGKANG SSAIFUTE INDUSTRIAL CO., LTD</t>
+  </si>
+  <si>
+    <t>ind</t>
+  </si>
+  <si>
+    <t>ind765</t>
+  </si>
+  <si>
+    <t>C000331 - INDUSTRIAL WEAR S.R.L.</t>
+  </si>
+  <si>
+    <t>sol</t>
+  </si>
+  <si>
+    <t>sol818</t>
+  </si>
+  <si>
+    <t>C000362 - SOLDINI F.LLI SPA</t>
+  </si>
+  <si>
+    <t>sup</t>
+  </si>
+  <si>
+    <t>sup658</t>
+  </si>
+  <si>
+    <t>C000371 - SUPER TANNERY LTD</t>
+  </si>
+  <si>
+    <t>qua</t>
+  </si>
+  <si>
+    <t>qua529</t>
+  </si>
+  <si>
+    <t>C000383 - QUALISHOE, LDA.</t>
+  </si>
+  <si>
+    <t>tre</t>
+  </si>
+  <si>
+    <t>tre325</t>
+  </si>
+  <si>
+    <t>C000394 - TRE VI Stampi SRL di Vigolo Alessandro &amp; C.</t>
+  </si>
+  <si>
+    <t>uve</t>
+  </si>
+  <si>
+    <t>uve559</t>
+  </si>
+  <si>
+    <t>C000401 - UVEX-CAGI S.R.L.</t>
+  </si>
+  <si>
+    <t>soc</t>
+  </si>
+  <si>
+    <t>soc703</t>
+  </si>
+  <si>
+    <t>C000441 - SOCIETE GREEN SECURITY</t>
+  </si>
+  <si>
+    <t>kfz</t>
+  </si>
+  <si>
+    <t>kfz384</t>
+  </si>
+  <si>
+    <t>C000457 - KFZ-M</t>
+  </si>
+  <si>
+    <t>cal4</t>
+  </si>
+  <si>
+    <t>cal928</t>
+  </si>
+  <si>
+    <t>C000581 - CALZATURIFICIO SKANDIA SPA</t>
+  </si>
+  <si>
+    <t>com</t>
+  </si>
+  <si>
+    <t>com990</t>
+  </si>
+  <si>
+    <t>C000599 - COMPOSTELLA SRL</t>
+  </si>
+  <si>
+    <t>tal</t>
+  </si>
+  <si>
+    <t>tal106</t>
+  </si>
+  <si>
+    <t>C000617 - TALANLEGPROM LTD.</t>
+  </si>
+  <si>
+    <t>res</t>
+  </si>
+  <si>
+    <t>res877</t>
+  </si>
+  <si>
+    <t>C000639 - RESPIREX INTERNATIONAL LTD</t>
+  </si>
+  <si>
+    <t>ove2</t>
+  </si>
+  <si>
+    <t>ove925</t>
+  </si>
+  <si>
+    <t>C000641 - OVERSTAMPI SRL</t>
+  </si>
+  <si>
+    <t>tal2</t>
+  </si>
+  <si>
+    <t>tal263</t>
+  </si>
+  <si>
+    <t>C000650 - Talleres Aragui  sl</t>
+  </si>
+  <si>
+    <t>ind2</t>
+  </si>
+  <si>
+    <t>ind814</t>
+  </si>
+  <si>
+    <t>C000662 - INDUSTRIAL ZAPATERA S.A.</t>
+  </si>
+  <si>
+    <t>elt</t>
+  </si>
+  <si>
+    <t>elt532</t>
+  </si>
+  <si>
+    <t>C000672 - ELTEN GMBH</t>
+  </si>
+  <si>
+    <t>scp</t>
+  </si>
+  <si>
+    <t>scp448</t>
+  </si>
+  <si>
+    <t>C000674 - SC PVC COMPOUND SRL</t>
+  </si>
+  <si>
+    <t>ide</t>
+  </si>
+  <si>
+    <t>ide384</t>
+  </si>
+  <si>
+    <t>C000739 - IDECAL LTDA</t>
+  </si>
+  <si>
+    <t>dia</t>
+  </si>
+  <si>
+    <t>dia259</t>
+  </si>
+  <si>
+    <t>C000751 - Dias da Costa, Irmãos, Lda</t>
+  </si>
+  <si>
+    <t>isc</t>
+  </si>
+  <si>
+    <t>isc320</t>
+  </si>
+  <si>
+    <t>C000766 - ISCO CELIK AYAK.TEKS.MAM.SAN.VE TIC.LTD.STI.</t>
+  </si>
+  <si>
+    <t>hai</t>
+  </si>
+  <si>
+    <t>hai881</t>
+  </si>
+  <si>
+    <t>C000780 - HAIX®-Schuhe Produktions- und Vertriebs GmbH</t>
+  </si>
+  <si>
+    <t>rep</t>
+  </si>
+  <si>
+    <t>rep444</t>
+  </si>
+  <si>
+    <t>C000791 - REPOSA SALES - GIANNONI GROUP SRL UNIPERSONALE</t>
+  </si>
+  <si>
+    <t>lex</t>
+  </si>
+  <si>
+    <t>lex204</t>
+  </si>
+  <si>
+    <t>C000796 - Lex International Pvt. Ltd</t>
+  </si>
+  <si>
+    <t>ann</t>
+  </si>
+  <si>
+    <t>ann194</t>
+  </si>
+  <si>
+    <t>C000824 - ANNABELLA SPA</t>
+  </si>
+  <si>
+    <t>cal5</t>
+  </si>
+  <si>
+    <t>cal489</t>
+  </si>
+  <si>
+    <t>C000836 - CALZATURIFICIO ZAMBERLAN S.R.L.</t>
+  </si>
+  <si>
+    <t>kla</t>
+  </si>
+  <si>
+    <t>kla199</t>
+  </si>
+  <si>
+    <t>C000839 - Klaus Ludwig GmbH &amp; Co. KG</t>
+  </si>
+  <si>
+    <t>pol</t>
+  </si>
+  <si>
+    <t>pol467</t>
+  </si>
+  <si>
+    <t>C000842 - POLYVER SWEDEN AB</t>
+  </si>
+  <si>
+    <t>chi</t>
+  </si>
+  <si>
+    <t>chi967</t>
+  </si>
+  <si>
+    <t>C000858 - CHIARAMONTE SRL</t>
+  </si>
+  <si>
+    <t>isc2</t>
+  </si>
+  <si>
+    <t>isc452</t>
+  </si>
+  <si>
+    <t>C000859 - ISCO Metal Urunleri San.veTic.Ltd.Sti</t>
+  </si>
+  <si>
+    <t>hum</t>
+  </si>
+  <si>
+    <t>hum718</t>
+  </si>
+  <si>
+    <t>C000864 - HUMEAU-BEAUPREAU SAS</t>
+  </si>
+  <si>
+    <t>sic</t>
+  </si>
+  <si>
+    <t>sic370</t>
+  </si>
+  <si>
+    <t>C000913 - SICILSERRA SRL</t>
+  </si>
+  <si>
+    <t>arm</t>
+  </si>
+  <si>
+    <t>arm926</t>
+  </si>
+  <si>
+    <t>C000928 - ARMOND S.R.L.</t>
+  </si>
+  <si>
+    <t>cal6</t>
+  </si>
+  <si>
+    <t>cal144</t>
+  </si>
+  <si>
+    <t>C000937 - CALZATURIFICIO TREEMME SRL</t>
+  </si>
+  <si>
+    <t>rou</t>
+  </si>
+  <si>
+    <t>rou847</t>
+  </si>
+  <si>
+    <t>C000942 - ROUTIER GROUP S.R.L.</t>
+  </si>
+  <si>
+    <t>scr</t>
+  </si>
+  <si>
+    <t>scr570</t>
+  </si>
+  <si>
+    <t>C000945 - SC REKORD SRL</t>
+  </si>
+  <si>
+    <t>zil</t>
+  </si>
+  <si>
+    <t>zil649</t>
+  </si>
+  <si>
+    <t>C000946 - ZILIO FABIO</t>
+  </si>
+  <si>
+    <t>far</t>
+  </si>
+  <si>
+    <t>far227</t>
+  </si>
+  <si>
+    <t>C000967 - FARRONATO MASSIMO</t>
+  </si>
+  <si>
+    <t>par</t>
+  </si>
+  <si>
+    <t>par487</t>
+  </si>
+  <si>
+    <t>C000971 - PAROLIN SOFIA</t>
+  </si>
+  <si>
+    <t>zur</t>
+  </si>
+  <si>
+    <t>zur180</t>
+  </si>
+  <si>
+    <t>C000974 - ZURLO MAURO</t>
+  </si>
+  <si>
+    <t>ugr</t>
+  </si>
+  <si>
+    <t>ugr665</t>
+  </si>
+  <si>
+    <t>C000994 - U GROUP S.R.L.</t>
+  </si>
+  <si>
+    <t>sup2</t>
+  </si>
+  <si>
+    <t>sup400</t>
+  </si>
+  <si>
+    <t>C001001 - SUPERHOUSE LIMITED (Safety Division)</t>
+  </si>
+  <si>
+    <t>ins</t>
+  </si>
+  <si>
+    <t>ins949</t>
+  </si>
+  <si>
+    <t>C001021 - INSPEC INTERNATIONAL LTD</t>
+  </si>
+  <si>
+    <t>nic</t>
+  </si>
+  <si>
+    <t>nic743</t>
+  </si>
+  <si>
+    <t>C001027 - NICAM Safety S.r.l.</t>
+  </si>
+  <si>
+    <t>gae</t>
+  </si>
+  <si>
+    <t>gae733</t>
+  </si>
+  <si>
+    <t>C001028 - GAERNE SPA</t>
+  </si>
+  <si>
+    <t>bor</t>
+  </si>
+  <si>
+    <t>bor982</t>
+  </si>
+  <si>
+    <t>C001041 - BORATTO MICHAEL</t>
+  </si>
+  <si>
+    <t>mor</t>
+  </si>
+  <si>
+    <t>mor470</t>
+  </si>
+  <si>
+    <t>C001047 - MORO MATTIA</t>
+  </si>
+  <si>
+    <t>kos</t>
+  </si>
+  <si>
+    <t>kos691</t>
+  </si>
+  <si>
+    <t>C001056 - KOSTIC NIKOLA</t>
+  </si>
+  <si>
+    <t>lap</t>
+  </si>
+  <si>
+    <t>lap296</t>
+  </si>
+  <si>
+    <t>C001059 - LA PAGANELLA SNC</t>
+  </si>
+  <si>
+    <t>wou</t>
+  </si>
+  <si>
+    <t>wou821</t>
+  </si>
+  <si>
+    <t>C001061 - WOUTER VAN BIJSTERVELD</t>
+  </si>
+  <si>
+    <t>stu</t>
+  </si>
+  <si>
+    <t>stu171</t>
+  </si>
+  <si>
+    <t>C001064 - STUCO KFT.</t>
+  </si>
+  <si>
+    <t>sap</t>
+  </si>
+  <si>
+    <t>sap146</t>
+  </si>
+  <si>
+    <t>C001075 - SAPRO SYSTEM Sp. z o. o.</t>
+  </si>
+  <si>
+    <t>mon</t>
+  </si>
+  <si>
+    <t>mon777</t>
+  </si>
+  <si>
+    <t>C001078 - MONDEOX SRL</t>
+  </si>
+  <si>
+    <t>jel</t>
+  </si>
+  <si>
+    <t>jel333</t>
+  </si>
+  <si>
+    <t>C001087 - Jelen Professional d.o.o.</t>
+  </si>
+  <si>
+    <t>lmg</t>
+  </si>
+  <si>
+    <t>lmg891</t>
+  </si>
+  <si>
+    <t>C001088 - LMG Spólka z ograniczonà odpowiedzialnoscià Sp. K.</t>
+  </si>
+  <si>
+    <t>sil</t>
+  </si>
+  <si>
+    <t>sil396</t>
+  </si>
+  <si>
+    <t>C001090 - SILVESTRI PAOLO</t>
+  </si>
+  <si>
+    <t>fle</t>
+  </si>
+  <si>
+    <t>fle181</t>
+  </si>
+  <si>
+    <t>C001095 - FLEX LINE SRL</t>
+  </si>
+  <si>
+    <t>sac</t>
+  </si>
+  <si>
+    <t>sac975</t>
+  </si>
+  <si>
+    <t>C001096 - SACI INTERNATIONAL LONGSTONE GROUP SRL</t>
+  </si>
+  <si>
+    <t>cal7</t>
+  </si>
+  <si>
+    <t>cal338</t>
+  </si>
+  <si>
+    <t>C001099 - Calzados Robusta S.L.</t>
+  </si>
+  <si>
+    <t>pss</t>
+  </si>
+  <si>
+    <t>pss987</t>
+  </si>
+  <si>
+    <t>C001109 - PSS Pfeiffer Sicherheitssysteme GmbH</t>
+  </si>
+  <si>
+    <t>jol</t>
+  </si>
+  <si>
+    <t>jol203</t>
+  </si>
+  <si>
+    <t>C001112 - JOLLY SCARPE ROMANIA SRL</t>
+  </si>
+  <si>
+    <t>ond</t>
+  </si>
+  <si>
+    <t>ond489</t>
+  </si>
+  <si>
+    <t>C001116 - ONDA doo</t>
+  </si>
+  <si>
+    <t>glo</t>
+  </si>
+  <si>
+    <t>glo384</t>
+  </si>
+  <si>
+    <t>C001123 - GLOBAL EXPORTS (SHOE DIVISION)</t>
+  </si>
+  <si>
+    <t>wss</t>
+  </si>
+  <si>
+    <t>wss564</t>
+  </si>
+  <si>
+    <t>C001145 - WSSC GmbH</t>
+  </si>
+  <si>
+    <t>ham</t>
+  </si>
+  <si>
+    <t>ham750</t>
+  </si>
+  <si>
+    <t>C001151 - HAMTECH</t>
+  </si>
+  <si>
+    <t>sun</t>
+  </si>
+  <si>
+    <t>sun954</t>
+  </si>
+  <si>
+    <t>C001159 - SUNSHINE TRADE</t>
+  </si>
+  <si>
+    <t>ret</t>
+  </si>
+  <si>
+    <t>ret473</t>
+  </si>
+  <si>
+    <t>C001161 - RETRYVER</t>
+  </si>
+  <si>
+    <t>btl</t>
+  </si>
+  <si>
+    <t>btl266</t>
+  </si>
+  <si>
+    <t>C001163 - BTL STEEL s.r.l.</t>
+  </si>
+  <si>
+    <t>saf</t>
+  </si>
+  <si>
+    <t>saf479</t>
+  </si>
+  <si>
+    <t>C001164 - SAFIT IB S.R.L.</t>
+  </si>
+  <si>
+    <t>ven</t>
+  </si>
+  <si>
+    <t>ven463</t>
+  </si>
+  <si>
+    <t>C001165 - VENETO.IT  d.o.o.</t>
+  </si>
+  <si>
+    <t>eve</t>
+  </si>
+  <si>
+    <t>eve314</t>
+  </si>
+  <si>
+    <t>C001166 - EVER TOP COMPANY LLC</t>
+  </si>
+  <si>
+    <t>chi2</t>
+  </si>
+  <si>
+    <t>chi786</t>
+  </si>
+  <si>
+    <t>C001169 - Chinook Asia</t>
+  </si>
+  <si>
+    <t>zak</t>
+  </si>
+  <si>
+    <t>zak373</t>
+  </si>
+  <si>
+    <t>C001170 - ZAK S.A.S. DI ZACCAGNI GIOVANNI</t>
+  </si>
+  <si>
+    <t>hug</t>
+  </si>
+  <si>
+    <t>hug818</t>
+  </si>
+  <si>
+    <t>C001174 - Hugo Star Trading LLC.</t>
+  </si>
+  <si>
+    <t>sar</t>
+  </si>
+  <si>
+    <t>sar799</t>
+  </si>
+  <si>
+    <t>C001175 - SARL HAMTECH POLYMERS</t>
+  </si>
+  <si>
     <t>stefano</t>
   </si>
   <si>
     <t>ste123</t>
+  </si>
+  <si>
+    <t>valentina</t>
+  </si>
+  <si>
+    <t>vale001</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -264,13 +1182,28 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <sz val="10"/>
-      <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -279,41 +1212,33 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF1F4E79"/>
+        <bgColor rgb="FF1F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE6F1"/>
+        <bgColor rgb="FFDCE6F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE699"/>
+        <bgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -322,27 +1247,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -678,15 +1595,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E837CC2E-FFAA-493E-9E03-C350178C8C16}">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D126"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="19.28515625" customWidth="1"/>
-    <col min="3" max="3" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="55" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>65</v>
       </c>
@@ -700,46 +1618,46 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="5">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="D2" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="5">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="D3" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="5">
-        <v>46084</v>
+      <c r="D4" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -749,277 +1667,1709 @@
       <c r="B5" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="6">
-        <v>46084</v>
+      <c r="D5" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="6">
-        <v>46084</v>
+      <c r="D6" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="8">
-        <v>46084</v>
+      <c r="D7" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="6">
-        <v>46084</v>
+      <c r="D8" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="6">
-        <v>46084</v>
+      <c r="D9" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="6">
-        <v>46084</v>
+      <c r="D10" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="A11" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="6">
-        <v>46084</v>
+      <c r="D11" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="6">
-        <v>46084</v>
+      <c r="D12" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="A13" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="6">
-        <v>46084</v>
+      <c r="D13" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="A14" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="6">
-        <v>46084</v>
+      <c r="D14" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="A15" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="6">
-        <v>46084</v>
+      <c r="D15" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="A16" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="6">
-        <v>46084</v>
+      <c r="D16" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="A17" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="6">
-        <v>46084</v>
+      <c r="D17" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="A18" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="6">
-        <v>46084</v>
+      <c r="D18" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="A19" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="6">
-        <v>46084</v>
+      <c r="D19" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="A20" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="6">
-        <v>46084</v>
+      <c r="D20" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="A21" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D21" s="6">
-        <v>46084</v>
+      <c r="D21" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="A22" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B123" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C123" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D22" s="6">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="D123" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B124" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C124" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D23" s="6">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>69</v>
-      </c>
-      <c r="B24" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="D124" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="C125" s="4" t="s">
         <v>2</v>
       </c>
+      <c r="D125" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>69</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/utenti.xlsx
+++ b/utenti.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF75F99-9BF2-45A1-BDE8-2FDB021E63F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{045DA3A2-139F-47AC-AF74-2CEF5CC4F76F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="1140" windowWidth="26100" windowHeight="13320" xr2:uid="{38FE3314-E022-4CA1-9956-19B554EBCB7E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{38FE3314-E022-4CA1-9956-19B554EBCB7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="382">
   <si>
     <t>safit_admin</t>
   </si>
@@ -1167,6 +1167,21 @@
   </si>
   <si>
     <t>vale001</t>
+  </si>
+  <si>
+    <t>03/03/2027</t>
+  </si>
+  <si>
+    <t>03/03/2028</t>
+  </si>
+  <si>
+    <t>btl2026</t>
+  </si>
+  <si>
+    <t>atoplast</t>
+  </si>
+  <si>
+    <t>atoplast2026</t>
   </si>
 </sst>
 </file>
@@ -1595,7 +1610,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E837CC2E-FFAA-493E-9E03-C350178C8C16}">
-  <dimension ref="A1:D126"/>
+  <dimension ref="A1:D128"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -3368,6 +3383,34 @@
         <v>69</v>
       </c>
     </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D127" s="4" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D128" s="4" t="s">
+        <v>378</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/utenti.xlsx
+++ b/utenti.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{045DA3A2-139F-47AC-AF74-2CEF5CC4F76F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB610A2E-70DD-4070-B791-FAA30E224DED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{38FE3314-E022-4CA1-9956-19B554EBCB7E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="384">
   <si>
     <t>safit_admin</t>
   </si>
@@ -1182,6 +1182,12 @@
   </si>
   <si>
     <t>atoplast2026</t>
+  </si>
+  <si>
+    <t>F001793 - BTL STEEL s.r.l.</t>
+  </si>
+  <si>
+    <t>F000072 - ATOPLAST SRL</t>
   </si>
 </sst>
 </file>
@@ -3391,7 +3397,7 @@
         <v>379</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>2</v>
+        <v>382</v>
       </c>
       <c r="D127" s="4" t="s">
         <v>377</v>
@@ -3405,7 +3411,7 @@
         <v>381</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>2</v>
+        <v>383</v>
       </c>
       <c r="D128" s="4" t="s">
         <v>378</v>

--- a/utenti.xlsx
+++ b/utenti.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB610A2E-70DD-4070-B791-FAA30E224DED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB6B817E-F036-40B4-9DB9-281E3B3B400B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{38FE3314-E022-4CA1-9956-19B554EBCB7E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="382">
   <si>
     <t>safit_admin</t>
   </si>
@@ -1086,12 +1086,6 @@
   </si>
   <si>
     <t>btl</t>
-  </si>
-  <si>
-    <t>btl266</t>
-  </si>
-  <si>
-    <t>C001163 - BTL STEEL s.r.l.</t>
   </si>
   <si>
     <t>saf</t>
@@ -3222,28 +3216,20 @@
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A115" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="C115" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="D115" s="3" t="s">
-        <v>69</v>
-      </c>
+      <c r="A115" s="3"/>
+      <c r="B115" s="3"/>
+      <c r="C115" s="3"/>
+      <c r="D115" s="3"/>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="C116" s="2" t="s">
         <v>352</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>354</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>69</v>
@@ -3251,13 +3237,13 @@
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C117" s="3" t="s">
         <v>355</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>357</v>
       </c>
       <c r="D117" s="3" t="s">
         <v>69</v>
@@ -3265,13 +3251,13 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C118" s="2" t="s">
         <v>358</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>360</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>69</v>
@@ -3279,13 +3265,13 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="C119" s="3" t="s">
         <v>361</v>
-      </c>
-      <c r="B119" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="C119" s="3" t="s">
-        <v>363</v>
       </c>
       <c r="D119" s="3" t="s">
         <v>69</v>
@@ -3293,13 +3279,13 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C120" s="2" t="s">
         <v>364</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>366</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>69</v>
@@ -3307,13 +3293,13 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="C121" s="3" t="s">
         <v>367</v>
-      </c>
-      <c r="B121" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="C121" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="D121" s="3" t="s">
         <v>69</v>
@@ -3321,13 +3307,13 @@
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="C122" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="B122" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>372</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>69</v>
@@ -3363,10 +3349,10 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>2</v>
@@ -3377,10 +3363,10 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>2</v>
@@ -3394,27 +3380,27 @@
         <v>349</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B128" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="C128" s="4" t="s">
         <v>381</v>
       </c>
-      <c r="C128" s="4" t="s">
-        <v>383</v>
-      </c>
       <c r="D128" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>

--- a/utenti.xlsx
+++ b/utenti.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB6B817E-F036-40B4-9DB9-281E3B3B400B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6080AFC2-07B8-4D09-8BDA-E2C31212DF79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{38FE3314-E022-4CA1-9956-19B554EBCB7E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="382">
   <si>
     <t>safit_admin</t>
   </si>
@@ -1163,12 +1163,6 @@
     <t>vale001</t>
   </si>
   <si>
-    <t>03/03/2027</t>
-  </si>
-  <si>
-    <t>03/03/2028</t>
-  </si>
-  <si>
     <t>btl2026</t>
   </si>
   <si>
@@ -1182,6 +1176,12 @@
   </si>
   <si>
     <t>F000072 - ATOPLAST SRL</t>
+  </si>
+  <si>
+    <t>guido</t>
+  </si>
+  <si>
+    <t>gui2026</t>
   </si>
 </sst>
 </file>
@@ -1262,7 +1262,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1276,6 +1276,7 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1610,7 +1611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E837CC2E-FFAA-493E-9E03-C350178C8C16}">
-  <dimension ref="A1:D128"/>
+  <dimension ref="A1:D129"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -3380,27 +3381,41 @@
         <v>349</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>375</v>
+        <v>69</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B128" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="C128" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="C128" s="4" t="s">
+      <c r="D128" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="B129" s="4" t="s">
         <v>381</v>
       </c>
-      <c r="D128" s="4" t="s">
-        <v>376</v>
+      <c r="C129" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D129" s="5">
+        <v>46115</v>
       </c>
     </row>
   </sheetData>

--- a/utenti.xlsx
+++ b/utenti.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6080AFC2-07B8-4D09-8BDA-E2C31212DF79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FDA3082-B973-4CBA-A8F1-9824FFDC10B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{38FE3314-E022-4CA1-9956-19B554EBCB7E}"/>
   </bookViews>
@@ -38,12 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="382">
   <si>
-    <t>safit_admin</t>
-  </si>
-  <si>
-    <t>admin2026</t>
-  </si>
-  <si>
     <t>TUTTI</t>
   </si>
   <si>
@@ -1182,6 +1176,12 @@
   </si>
   <si>
     <t>gui2026</t>
+  </si>
+  <si>
+    <t>Safit_admin</t>
+  </si>
+  <si>
+    <t>admin01</t>
   </si>
 </sst>
 </file>
@@ -1622,1598 +1622,1598 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="D22" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>75</v>
-      </c>
       <c r="D23" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="D24" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="D25" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="D26" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="D27" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="D28" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="D29" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>96</v>
-      </c>
       <c r="D30" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="D31" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="D32" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="D33" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="D34" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>111</v>
-      </c>
       <c r="D35" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>114</v>
-      </c>
       <c r="D36" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>117</v>
-      </c>
       <c r="D37" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="D38" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>123</v>
-      </c>
       <c r="D39" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>126</v>
-      </c>
       <c r="D40" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="D41" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="D42" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="D43" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>138</v>
-      </c>
       <c r="D44" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="D45" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>144</v>
-      </c>
       <c r="D46" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>147</v>
-      </c>
       <c r="D47" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>150</v>
-      </c>
       <c r="D48" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>153</v>
-      </c>
       <c r="D49" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="D50" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>159</v>
-      </c>
       <c r="D51" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="D52" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>165</v>
-      </c>
       <c r="D53" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="D54" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>171</v>
-      </c>
       <c r="D55" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>174</v>
-      </c>
       <c r="D56" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>177</v>
-      </c>
       <c r="D57" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>180</v>
-      </c>
       <c r="D58" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B59" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>183</v>
-      </c>
       <c r="D59" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>186</v>
-      </c>
       <c r="D60" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C61" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="B61" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>189</v>
-      </c>
       <c r="D61" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>192</v>
-      </c>
       <c r="D62" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="B63" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>195</v>
-      </c>
       <c r="D63" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>198</v>
-      </c>
       <c r="D64" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C65" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="B65" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>201</v>
-      </c>
       <c r="D65" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C66" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>204</v>
-      </c>
       <c r="D66" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C67" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B67" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="D67" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>210</v>
-      </c>
       <c r="D68" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B69" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>213</v>
-      </c>
       <c r="D69" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="B70" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>216</v>
-      </c>
       <c r="D70" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C71" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="B71" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>219</v>
-      </c>
       <c r="D71" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>222</v>
-      </c>
       <c r="D72" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C73" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="B73" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>225</v>
-      </c>
       <c r="D73" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>228</v>
-      </c>
       <c r="D74" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C75" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="B75" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>231</v>
-      </c>
       <c r="D75" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C76" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="B76" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>234</v>
-      </c>
       <c r="D76" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="B77" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>237</v>
-      </c>
       <c r="D77" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C78" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="B78" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>240</v>
-      </c>
       <c r="D78" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="B79" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>243</v>
-      </c>
       <c r="D79" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C80" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>246</v>
-      </c>
       <c r="D80" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C81" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="B81" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>249</v>
-      </c>
       <c r="D81" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B82" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>252</v>
-      </c>
       <c r="D82" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B83" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>255</v>
-      </c>
       <c r="D83" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C84" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>258</v>
-      </c>
       <c r="D84" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C85" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="B85" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>261</v>
-      </c>
       <c r="D85" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C86" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="B86" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>264</v>
-      </c>
       <c r="D86" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C87" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="B87" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>267</v>
-      </c>
       <c r="D87" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C88" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>270</v>
-      </c>
       <c r="D88" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C89" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="B89" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>273</v>
-      </c>
       <c r="D89" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C90" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="B90" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>276</v>
-      </c>
       <c r="D90" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C91" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="B91" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>279</v>
-      </c>
       <c r="D91" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C92" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="B92" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>282</v>
-      </c>
       <c r="D92" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C93" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="B93" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>285</v>
-      </c>
       <c r="D93" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C94" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B94" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>288</v>
-      </c>
       <c r="D94" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C95" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="B95" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>291</v>
-      </c>
       <c r="D95" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C96" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>294</v>
-      </c>
       <c r="D96" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C97" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="B97" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>297</v>
-      </c>
       <c r="D97" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C98" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="B98" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>300</v>
-      </c>
       <c r="D98" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="C99" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="B99" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>303</v>
-      </c>
       <c r="D99" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C100" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="B100" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>306</v>
-      </c>
       <c r="D100" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C101" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="B101" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>309</v>
-      </c>
       <c r="D101" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C102" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B102" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>312</v>
-      </c>
       <c r="D102" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="C103" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="B103" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>315</v>
-      </c>
       <c r="D103" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C104" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="B104" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>318</v>
-      </c>
       <c r="D104" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C105" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="B105" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>321</v>
-      </c>
       <c r="D105" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C106" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="B106" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>324</v>
-      </c>
       <c r="D106" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C107" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="B107" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="C107" s="3" t="s">
-        <v>327</v>
-      </c>
       <c r="D107" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C108" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="B108" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>330</v>
-      </c>
       <c r="D108" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="C109" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="B109" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="C109" s="3" t="s">
-        <v>333</v>
-      </c>
       <c r="D109" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="C110" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="B110" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>336</v>
-      </c>
       <c r="D110" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C111" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="B111" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="C111" s="3" t="s">
-        <v>339</v>
-      </c>
       <c r="D111" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C112" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B112" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>342</v>
-      </c>
       <c r="D112" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C113" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="B113" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="C113" s="3" t="s">
-        <v>345</v>
-      </c>
       <c r="D113" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C114" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="B114" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>348</v>
-      </c>
       <c r="D114" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
@@ -3224,195 +3224,195 @@
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="C116" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="B116" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>352</v>
-      </c>
       <c r="D116" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C117" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="B117" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>355</v>
-      </c>
       <c r="D117" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="C118" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="B118" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>358</v>
-      </c>
       <c r="D118" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C119" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="B119" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="C119" s="3" t="s">
-        <v>361</v>
-      </c>
       <c r="D119" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C120" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="B120" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>364</v>
-      </c>
       <c r="D120" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="C121" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="B121" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="C121" s="3" t="s">
-        <v>367</v>
-      </c>
       <c r="D121" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="C122" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="B122" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>370</v>
-      </c>
       <c r="D122" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="C123" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B123" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C123" s="4" t="s">
-        <v>2</v>
-      </c>
       <c r="D123" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B128" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="C128" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="C128" s="4" t="s">
-        <v>379</v>
-      </c>
       <c r="D128" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D129" s="5">
         <v>46115</v>

--- a/utenti.xlsx
+++ b/utenti.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FDA3082-B973-4CBA-A8F1-9824FFDC10B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DF2A940-91F5-430A-BA6E-8D6A923336D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{38FE3314-E022-4CA1-9956-19B554EBCB7E}"/>
   </bookViews>

--- a/utenti.xlsx
+++ b/utenti.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DF2A940-91F5-430A-BA6E-8D6A923336D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EADE04C-4890-4B83-9612-C8727E172E78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{38FE3314-E022-4CA1-9956-19B554EBCB7E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="384">
   <si>
     <t>TUTTI</t>
   </si>
@@ -1182,6 +1182,12 @@
   </si>
   <si>
     <t>admin01</t>
+  </si>
+  <si>
+    <t>zak799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F001819 - ZAK S.A.S. DI ZACCAGNI GIOVANNI            </t>
   </si>
 </sst>
 </file>
@@ -3217,115 +3223,123 @@
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A115" s="3"/>
-      <c r="B115" s="3"/>
-      <c r="C115" s="3"/>
-      <c r="D115" s="3"/>
+      <c r="A115" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A116" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="D116" s="2" t="s">
+      <c r="A116" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="D116" s="3" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A117" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="D117" s="3" t="s">
+      <c r="A117" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="D117" s="2" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A118" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="D118" s="2" t="s">
+      <c r="A118" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="D118" s="3" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A119" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="B119" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="C119" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="D119" s="3" t="s">
+      <c r="A119" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D119" s="2" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A120" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="D120" s="2" t="s">
+      <c r="A120" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="D120" s="3" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A121" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="B121" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="C121" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="D121" s="3" t="s">
+      <c r="A121" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D121" s="2" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A122" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B122" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="D122" s="2" t="s">
+      <c r="A122" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D122" s="4" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
-        <v>380</v>
+        <v>6</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>381</v>
+        <v>42</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>0</v>
@@ -3336,10 +3350,10 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>6</v>
+        <v>369</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>42</v>
+        <v>370</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>0</v>
@@ -3350,10 +3364,10 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>0</v>
@@ -3364,13 +3378,13 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>371</v>
+        <v>347</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>0</v>
+        <v>376</v>
       </c>
       <c r="D126" s="4" t="s">
         <v>67</v>
@@ -3378,13 +3392,13 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
-        <v>347</v>
+        <v>374</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D127" s="4" t="s">
         <v>67</v>
@@ -3392,30 +3406,30 @@
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>377</v>
-      </c>
-      <c r="D128" s="4" t="s">
-        <v>67</v>
+        <v>0</v>
+      </c>
+      <c r="D128" s="5">
+        <v>46115</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>0</v>
+        <v>383</v>
       </c>
       <c r="D129" s="5">
-        <v>46115</v>
+        <v>46132</v>
       </c>
     </row>
   </sheetData>

--- a/utenti.xlsx
+++ b/utenti.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Venezian.Denis\Desktop\python_access_sql\git-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EADE04C-4890-4B83-9612-C8727E172E78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4935AAF1-ED44-47C7-88F4-16739834F5CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{38FE3314-E022-4CA1-9956-19B554EBCB7E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="382">
   <si>
     <t>TUTTI</t>
   </si>
@@ -1143,12 +1143,6 @@
   </si>
   <si>
     <t>C001175 - SARL HAMTECH POLYMERS</t>
-  </si>
-  <si>
-    <t>stefano</t>
-  </si>
-  <si>
-    <t>ste123</t>
   </si>
   <si>
     <t>valentina</t>
@@ -1617,7 +1611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E837CC2E-FFAA-493E-9E03-C350178C8C16}">
-  <dimension ref="A1:D129"/>
+  <dimension ref="A1:D128"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -3322,10 +3316,10 @@
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>0</v>
@@ -3364,13 +3358,13 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="B125" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="B125" s="4" t="s">
-        <v>372</v>
-      </c>
       <c r="C125" s="4" t="s">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="D125" s="4" t="s">
         <v>67</v>
@@ -3378,13 +3372,13 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>347</v>
+        <v>372</v>
       </c>
       <c r="B126" s="4" t="s">
         <v>373</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D126" s="4" t="s">
         <v>67</v>
@@ -3392,43 +3386,29 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>377</v>
-      </c>
-      <c r="D127" s="4" t="s">
-        <v>67</v>
+        <v>0</v>
+      </c>
+      <c r="D127" s="5">
+        <v>46115</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>0</v>
+        <v>381</v>
       </c>
       <c r="D128" s="5">
-        <v>46115</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A129" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="B129" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="C129" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="D129" s="5">
         <v>46132</v>
       </c>
     </row>
